--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9284,0.0220,0.0098,0.0248</t>
-  </si>
-  <si>
-    <t>0.0108,0.0003,0.0005,0.9958</t>
-  </si>
-  <si>
-    <t>0.9278,0.0063,0.0008,0.0401</t>
-  </si>
-  <si>
-    <t>0.4732,0.0039,0.0006,0.7139</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9972,0.0011,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9932,0.0064,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0005,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.8200,0.0340,0.1733,0.0039</t>
-  </si>
-  <si>
-    <t>0.0487,0.0116,0.9487,0.0027</t>
-  </si>
-  <si>
-    <t>0.4081,0.0026,0.7170,0.0012</t>
-  </si>
-  <si>
-    <t>0.0137,0.0013,0.9870,0.0025</t>
-  </si>
-  <si>
-    <t>0.9349,0.0191,0.0189,0.0032</t>
-  </si>
-  <si>
-    <t>0.0007,0.9980,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.9875,0.0024,0.0019</t>
-  </si>
-  <si>
-    <t>0.0769,0.9273,0.0039,0.0014</t>
-  </si>
-  <si>
-    <t>0.0180,0.9737,0.0104,0.0013</t>
-  </si>
-  <si>
-    <t>0.0006,0.9979,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.8793,0.0008,0.1354,0.0038</t>
-  </si>
-  <si>
-    <t>0.8320,0.0132,0.1757,0.0022</t>
-  </si>
-  <si>
-    <t>0.0133,0.0006,0.9878,0.0012</t>
-  </si>
-  <si>
-    <t>0.0738,0.0063,0.9456,0.0018</t>
-  </si>
-  <si>
-    <t>0.1254,0.0025,0.9463,0.0008</t>
-  </si>
-  <si>
-    <t>0.0908,0.0030,0.9410,0.0083</t>
-  </si>
-  <si>
-    <t>0.0182,0.0016,0.9905,0.0006</t>
-  </si>
-  <si>
-    <t>0.7578,0.2492,0.0310,0.0124</t>
-  </si>
-  <si>
-    <t>0.0971,0.7309,0.2952,0.0073</t>
-  </si>
-  <si>
-    <t>0.0008,0.0206,0.9980,0.0017</t>
-  </si>
-  <si>
-    <t>0.0077,0.9745,0.0337,0.0006</t>
-  </si>
-  <si>
-    <t>0.8342,0.0549,0.1097,0.0365</t>
-  </si>
-  <si>
-    <t>0.8389,0.0117,0.1048,0.0096</t>
-  </si>
-  <si>
-    <t>0.7855,0.2900,0.0026,0.0014</t>
-  </si>
-  <si>
-    <t>0.0236,0.9571,0.1512,0.0032</t>
-  </si>
-  <si>
-    <t>0.0071,0.0456,0.8617,0.0262</t>
-  </si>
-  <si>
-    <t>0.0068,0.0001,0.7303,0.1116</t>
-  </si>
-  <si>
-    <t>0.0244,0.0082,0.9729,0.0028</t>
-  </si>
-  <si>
-    <t>0.0123,0.0049,0.7792,0.3914</t>
-  </si>
-  <si>
-    <t>0.0157,0.1843,0.9656,0.0020</t>
-  </si>
-  <si>
-    <t>0.0224,0.9661,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.0076,0.0638,0.9640,0.0078</t>
-  </si>
-  <si>
-    <t>0.0095,0.7714,0.0043,0.7986</t>
-  </si>
-  <si>
-    <t>0.0098,0.9521,0.0184,0.0780</t>
-  </si>
-  <si>
-    <t>0.0106,0.9758,0.0130,0.0017</t>
-  </si>
-  <si>
-    <t>0.0086,0.9785,0.0776,0.0028</t>
-  </si>
-  <si>
-    <t>0.0021,0.0200,0.9891,0.0037</t>
-  </si>
-  <si>
-    <t>0.0022,0.0268,0.9965,0.0003</t>
-  </si>
-  <si>
-    <t>0.0163,0.0026,0.9736,0.0097</t>
-  </si>
-  <si>
-    <t>0.0077,0.0006,0.9949,0.0004</t>
-  </si>
-  <si>
-    <t>0.0013,0.0020,0.9974,0.0008</t>
-  </si>
-  <si>
-    <t>0.0041,0.0297,0.9856,0.0033</t>
-  </si>
-  <si>
-    <t>0.9829,0.0174,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9707,0.0075,0.0109,0.0063</t>
-  </si>
-  <si>
-    <t>0.9948,0.0018,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.1137,0.9968,0.0189</t>
-  </si>
-  <si>
-    <t>0.9979,0.0005,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9972,0.0020,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0040,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.0014,0.5672,0.9957,0.0002</t>
-  </si>
-  <si>
-    <t>0.0073,0.1745,0.9733,0.0049</t>
-  </si>
-  <si>
-    <t>0.0022,0.0233,0.9731,0.0164</t>
-  </si>
-  <si>
-    <t>0.0015,0.9361,0.9624,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.0046,0.9951,0.0036</t>
-  </si>
-  <si>
-    <t>0.0280,0.9727,0.0079,0.0002</t>
-  </si>
-  <si>
-    <t>0.0042,0.9924,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.5911,0.0028,0.5671,0.0030</t>
-  </si>
-  <si>
-    <t>0.9149,0.0116,0.0897,0.0007</t>
-  </si>
-  <si>
-    <t>0.0130,0.0458,0.9740,0.0167</t>
-  </si>
-  <si>
-    <t>0.0011,0.9785,0.7417,0.0001</t>
-  </si>
-  <si>
-    <t>0.0048,0.9352,0.8024,0.0007</t>
-  </si>
-  <si>
-    <t>0.0026,0.9814,0.0876,0.0045</t>
-  </si>
-  <si>
-    <t>0.0036,0.9813,0.2959,0.0015</t>
-  </si>
-  <si>
-    <t>0.0024,0.0002,0.0028,0.9963</t>
-  </si>
-  <si>
-    <t>0.0011,0.0034,0.0000,0.9991</t>
-  </si>
-  <si>
-    <t>0.0090,0.0006,0.0005,0.9961</t>
-  </si>
-  <si>
-    <t>0.0114,0.0008,0.0019,0.9933</t>
-  </si>
-  <si>
-    <t>0.0048,0.0009,0.0007,0.9963</t>
-  </si>
-  <si>
-    <t>0.0039,0.0010,0.0003,0.9975</t>
-  </si>
-  <si>
-    <t>0.0027,0.9713,0.6651,0.0004</t>
-  </si>
-  <si>
-    <t>0.0025,0.7476,0.9864,0.0003</t>
-  </si>
-  <si>
-    <t>0.0079,0.8822,0.6163,0.0067</t>
-  </si>
-  <si>
-    <t>0.0027,0.9734,0.3526,0.0046</t>
-  </si>
-  <si>
-    <t>0.0017,0.8721,0.9633,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.9814,0.2988,0.0003</t>
-  </si>
-  <si>
-    <t>0.9942,0.0034,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9862,0.0160,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9918,0.0048,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9931,0.0029,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9971,0.0030,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0027,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9924,0.0025,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9894,0.0063,0.0017,0.0016</t>
-  </si>
-  <si>
-    <t>0.9958,0.0003,0.0001,0.0025</t>
-  </si>
-  <si>
-    <t>0.9947,0.0011,0.0002,0.0019</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0002,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9953,0.0009,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.0028,0.0008,0.9973,0.0011</t>
-  </si>
-  <si>
-    <t>0.0582,0.0027,0.9720,0.0004</t>
-  </si>
-  <si>
-    <t>0.9405,0.0012,0.0331,0.0033</t>
-  </si>
-  <si>
-    <t>0.0098,0.0006,0.9891,0.0029</t>
-  </si>
-  <si>
-    <t>0.0056,0.9887,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.0073,0.9865,0.0032,0.0008</t>
-  </si>
-  <si>
-    <t>0.0527,0.9522,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.0373,0.9581,0.0120,0.0006</t>
-  </si>
-  <si>
-    <t>0.0041,0.9903,0.0050,0.0014</t>
-  </si>
-  <si>
-    <t>0.0023,0.9935,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.2259,0.8599,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.7360,0.1352,0.0892,0.0273</t>
-  </si>
-  <si>
-    <t>0.8576,0.0045,0.1559,0.0041</t>
-  </si>
-  <si>
-    <t>0.6398,0.0460,0.3876,0.0133</t>
-  </si>
-  <si>
-    <t>0.3328,0.0156,0.7243,0.0103</t>
-  </si>
-  <si>
-    <t>0.1633,0.0721,0.0105,0.8092</t>
-  </si>
-  <si>
-    <t>0.0353,0.9591,0.0085,0.0008</t>
-  </si>
-  <si>
-    <t>0.0158,0.9689,0.0120,0.0019</t>
-  </si>
-  <si>
-    <t>0.0017,0.9928,0.0072,0.0056</t>
-  </si>
-  <si>
-    <t>0.0085,0.9587,0.6381,0.0025</t>
-  </si>
-  <si>
-    <t>0.0591,0.9380,0.0050,0.0016</t>
-  </si>
-  <si>
-    <t>0.1947,0.8616,0.0114,0.0015</t>
-  </si>
-  <si>
-    <t>0.9326,0.0632,0.0142,0.0021</t>
-  </si>
-  <si>
-    <t>0.9917,0.0011,0.0042,0.0006</t>
-  </si>
-  <si>
-    <t>0.9954,0.0004,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9952,0.0002,0.0001,0.0031</t>
-  </si>
-  <si>
-    <t>0.9808,0.0018,0.0012,0.0118</t>
-  </si>
-  <si>
-    <t>0.9960,0.0003,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9956,0.0005,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9936,0.0014,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.0015,0.5866,0.9894,0.0004</t>
-  </si>
-  <si>
-    <t>0.0068,0.2444,0.9693,0.0012</t>
-  </si>
-  <si>
-    <t>0.0084,0.0160,0.9845,0.0014</t>
-  </si>
-  <si>
-    <t>0.0035,0.0035,0.9930,0.0014</t>
-  </si>
-  <si>
-    <t>0.9385,0.0048,0.0237,0.0082</t>
-  </si>
-  <si>
-    <t>0.2145,0.0096,0.7815,0.0244</t>
-  </si>
-  <si>
-    <t>0.5142,0.0003,0.6668,0.0012</t>
-  </si>
-  <si>
-    <t>0.6144,0.0705,0.3607,0.0286</t>
-  </si>
-  <si>
-    <t>0.0142,0.0002,0.0002,0.9961</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0034,0.0002,0.0002,0.9984</t>
-  </si>
-  <si>
-    <t>0.0075,0.0006,0.0002,0.9975</t>
-  </si>
-  <si>
-    <t>0.0041,0.9078,0.7258,0.0016</t>
-  </si>
-  <si>
-    <t>0.9963,0.0008,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.0073,0.9787,0.0015,0.0265</t>
-  </si>
-  <si>
-    <t>0.9927,0.0012,0.0008,0.0022</t>
-  </si>
-  <si>
-    <t>0.5482,0.5086,0.0026,0.0090</t>
-  </si>
-  <si>
-    <t>0.9968,0.0006,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9743,0.0010,0.0014,0.0174</t>
-  </si>
-  <si>
-    <t>0.9967,0.0011,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.0039,0.6282,0.7453,0.0835</t>
-  </si>
-  <si>
-    <t>0.8986,0.0018,0.0040,0.1207</t>
-  </si>
-  <si>
-    <t>0.8761,0.0058,0.0234,0.0625</t>
-  </si>
-  <si>
-    <t>0.4147,0.6370,0.0249,0.0030</t>
-  </si>
-  <si>
-    <t>0.9897,0.0012,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.9791,0.0065,0.0059,0.0015</t>
-  </si>
-  <si>
-    <t>0.8039,0.2067,0.0144,0.0044</t>
-  </si>
-  <si>
-    <t>0.5592,0.2753,0.3047,0.0384</t>
-  </si>
-  <si>
-    <t>0.9618,0.0311,0.0058,0.0014</t>
-  </si>
-  <si>
-    <t>0.9882,0.0045,0.0016,0.0028</t>
-  </si>
-  <si>
-    <t>0.9964,0.0009,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9963,0.0010,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9919,0.0015,0.0010,0.0026</t>
-  </si>
-  <si>
-    <t>0.9950,0.0006,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9972,0.0004,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9970,0.0007,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9945,0.0009,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.2453,0.7575,0.0055,0.0022</t>
-  </si>
-  <si>
-    <t>0.4606,0.6220,0.0089,0.0009</t>
-  </si>
-  <si>
-    <t>0.8299,0.2578,0.0036,0.0012</t>
-  </si>
-  <si>
-    <t>0.0847,0.2104,0.8752,0.0072</t>
-  </si>
-  <si>
-    <t>0.9895,0.0108,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9848,0.0065,0.0045,0.0011</t>
-  </si>
-  <si>
-    <t>0.9767,0.0226,0.0043,0.0013</t>
-  </si>
-  <si>
-    <t>0.9820,0.0136,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.0022,0.0146,0.9967,0.0028</t>
-  </si>
-  <si>
-    <t>0.4682,0.4320,0.0004,0.0044</t>
-  </si>
-  <si>
-    <t>0.0011,0.0007,0.9972,0.0013</t>
-  </si>
-  <si>
-    <t>0.0036,0.1365,0.9835,0.0034</t>
-  </si>
-  <si>
-    <t>0.0076,0.0032,0.9888,0.0084</t>
-  </si>
-  <si>
-    <t>0.0062,0.0118,0.9834,0.0044</t>
-  </si>
-  <si>
-    <t>0.0128,0.0230,0.9686,0.0118</t>
-  </si>
-  <si>
-    <t>0.1114,0.0003,0.9497,0.0004</t>
-  </si>
-  <si>
-    <t>0.0056,0.0021,0.9938,0.0008</t>
-  </si>
-  <si>
-    <t>0.6307,0.0096,0.4780,0.0051</t>
-  </si>
-  <si>
-    <t>0.2529,0.0139,0.7969,0.0052</t>
-  </si>
-  <si>
-    <t>0.3283,0.2837,0.4293,0.0267</t>
-  </si>
-  <si>
-    <t>0.0659,0.1950,0.7812,0.0069</t>
-  </si>
-  <si>
-    <t>0.1234,0.3189,0.5936,0.0116</t>
-  </si>
-  <si>
-    <t>0.9207,0.0018,0.1180,0.0002</t>
-  </si>
-  <si>
-    <t>0.9254,0.0111,0.0406,0.0044</t>
-  </si>
-  <si>
-    <t>0.5102,0.0209,0.5462,0.0086</t>
-  </si>
-  <si>
-    <t>0.5322,0.5818,0.0060,0.0005</t>
-  </si>
-  <si>
-    <t>0.0285,0.9685,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9861,0.0102,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.6664,0.5063,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.9007,0.1643,0.0034,0.0008</t>
-  </si>
-  <si>
-    <t>0.9517,0.0180,0.0188,0.0006</t>
-  </si>
-  <si>
-    <t>0.9318,0.0016,0.0613,0.0027</t>
-  </si>
-  <si>
-    <t>0.9637,0.0176,0.0032,0.0029</t>
-  </si>
-  <si>
-    <t>0.9291,0.0014,0.0962,0.0010</t>
-  </si>
-  <si>
-    <t>0.8205,0.0144,0.1167,0.0317</t>
-  </si>
-  <si>
-    <t>0.0054,0.0030,0.9824,0.0484</t>
-  </si>
-  <si>
-    <t>0.0192,0.0714,0.9324,0.0139</t>
-  </si>
-  <si>
-    <t>0.0505,0.0727,0.8616,0.0192</t>
-  </si>
-  <si>
-    <t>0.1267,0.0008,0.9172,0.0011</t>
-  </si>
-  <si>
-    <t>0.0617,0.0977,0.8704,0.0186</t>
-  </si>
-  <si>
-    <t>0.9932,0.0013,0.0002,0.0033</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9917,0.0040,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9972,0.0014,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9920,0.0025,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.9958,0.0009,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9949,0.0004,0.0003,0.0031</t>
-  </si>
-  <si>
-    <t>0.9951,0.0009,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.0055,0.0161,0.9912,0.0055</t>
-  </si>
-  <si>
-    <t>0.2798,0.2619,0.5350,0.0485</t>
-  </si>
-  <si>
-    <t>0.9441,0.0074,0.0216,0.0110</t>
-  </si>
-  <si>
-    <t>0.0138,0.0070,0.9875,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.9932,0.0092</t>
-  </si>
-  <si>
-    <t>0.1215,0.1069,0.7029,0.0039</t>
-  </si>
-  <si>
-    <t>0.0018,0.0008,0.9984,0.0003</t>
-  </si>
-  <si>
-    <t>0.0072,0.0014,0.9936,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0051,0.0017,0.9942,0.0005</t>
-  </si>
-  <si>
-    <t>0.0562,0.0269,0.9375,0.0084</t>
-  </si>
-  <si>
-    <t>0.6266,0.0090,0.3410,0.0328</t>
-  </si>
-  <si>
-    <t>0.3796,0.0080,0.5640,0.0317</t>
-  </si>
-  <si>
-    <t>0.9881,0.0005,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.9858,0.0078,0.0013,0.0022</t>
-  </si>
-  <si>
-    <t>0.9944,0.0017,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0011,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9907,0.0072,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9950,0.0003,0.0001,0.0039</t>
-  </si>
-  <si>
-    <t>0.9941,0.0017,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9945,0.0031,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9911,0.0019,0.0008,0.0039</t>
-  </si>
-  <si>
-    <t>0.0097,0.2850,0.7448,0.0367</t>
-  </si>
-  <si>
-    <t>0.0125,0.0044,0.9866,0.0010</t>
-  </si>
-  <si>
-    <t>0.0119,0.1149,0.9467,0.0148</t>
-  </si>
-  <si>
-    <t>0.0456,0.0075,0.9651,0.0017</t>
-  </si>
-  <si>
-    <t>0.0073,0.0007,0.9920,0.0009</t>
-  </si>
-  <si>
-    <t>0.0778,0.0050,0.7478,0.1628</t>
-  </si>
-  <si>
-    <t>0.6044,0.0241,0.4119,0.0104</t>
-  </si>
-  <si>
-    <t>0.4551,0.0234,0.4678,0.0584</t>
-  </si>
-  <si>
-    <t>0.9817,0.0005,0.0009,0.0163</t>
-  </si>
-  <si>
-    <t>0.0875,0.0053,0.0022,0.9676</t>
-  </si>
-  <si>
-    <t>0.0118,0.0018,0.0027,0.9899</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0004,0.9993</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.0005,0.9992</t>
-  </si>
-  <si>
-    <t>0.9759,0.0021,0.0013,0.0165</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9636,0.0020,0.0031,0.0182</t>
+  </si>
+  <si>
+    <t>0.0053,0.0003,0.0000,0.9984</t>
+  </si>
+  <si>
+    <t>0.9331,0.0003,0.0001,0.1207</t>
+  </si>
+  <si>
+    <t>0.0252,0.0009,0.0010,0.9914</t>
+  </si>
+  <si>
+    <t>0.9968,0.0016,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9943,0.0028,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9942,0.0017,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9970,0.0007,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9921,0.0037,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.9939,0.0043,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0011,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.7224,0.0545,0.2672,0.0132</t>
+  </si>
+  <si>
+    <t>0.0455,0.0031,0.9620,0.0037</t>
+  </si>
+  <si>
+    <t>0.2109,0.0054,0.8765,0.0005</t>
+  </si>
+  <si>
+    <t>0.0177,0.0050,0.9798,0.0053</t>
+  </si>
+  <si>
+    <t>0.8510,0.0067,0.1548,0.0023</t>
+  </si>
+  <si>
+    <t>0.0132,0.9853,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.0061,0.9862,0.0020,0.0023</t>
+  </si>
+  <si>
+    <t>0.0398,0.9480,0.0087,0.0027</t>
+  </si>
+  <si>
+    <t>0.0153,0.9753,0.0208,0.0021</t>
+  </si>
+  <si>
+    <t>0.0006,0.9982,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9226,0.0017,0.0521,0.0055</t>
+  </si>
+  <si>
+    <t>0.8987,0.0018,0.1394,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9989,0.0004</t>
+  </si>
+  <si>
+    <t>0.0149,0.0155,0.9732,0.0061</t>
+  </si>
+  <si>
+    <t>0.0631,0.0008,0.9775,0.0003</t>
+  </si>
+  <si>
+    <t>0.1656,0.0014,0.8918,0.0040</t>
+  </si>
+  <si>
+    <t>0.0082,0.0042,0.9887,0.0030</t>
+  </si>
+  <si>
+    <t>0.8654,0.1802,0.0089,0.0016</t>
+  </si>
+  <si>
+    <t>0.6064,0.1901,0.2492,0.0087</t>
+  </si>
+  <si>
+    <t>0.0030,0.0045,0.9969,0.0011</t>
+  </si>
+  <si>
+    <t>0.0302,0.9248,0.0534,0.0008</t>
+  </si>
+  <si>
+    <t>0.9097,0.0780,0.0140,0.0112</t>
+  </si>
+  <si>
+    <t>0.3575,0.0077,0.7277,0.0068</t>
+  </si>
+  <si>
+    <t>0.6469,0.4655,0.0051,0.0018</t>
+  </si>
+  <si>
+    <t>0.0094,0.9725,0.2057,0.0008</t>
+  </si>
+  <si>
+    <t>0.0522,0.2723,0.6154,0.0130</t>
+  </si>
+  <si>
+    <t>0.2462,0.0081,0.5775,0.0509</t>
+  </si>
+  <si>
+    <t>0.2657,0.0014,0.8757,0.0006</t>
+  </si>
+  <si>
+    <t>0.7482,0.0009,0.2680,0.0040</t>
+  </si>
+  <si>
+    <t>0.0051,0.1029,0.9862,0.0033</t>
+  </si>
+  <si>
+    <t>0.0050,0.9864,0.0059,0.0004</t>
+  </si>
+  <si>
+    <t>0.0036,0.0034,0.9924,0.0017</t>
+  </si>
+  <si>
+    <t>0.0282,0.1721,0.0080,0.9394</t>
+  </si>
+  <si>
+    <t>0.0035,0.9827,0.0094,0.0324</t>
+  </si>
+  <si>
+    <t>0.0267,0.9213,0.0392,0.0220</t>
+  </si>
+  <si>
+    <t>0.0025,0.9945,0.0540,0.0002</t>
+  </si>
+  <si>
+    <t>0.0037,0.0217,0.9886,0.0016</t>
+  </si>
+  <si>
+    <t>0.0020,0.0385,0.9945,0.0006</t>
+  </si>
+  <si>
+    <t>0.0166,0.0063,0.9694,0.0257</t>
+  </si>
+  <si>
+    <t>0.0077,0.0005,0.9947,0.0007</t>
+  </si>
+  <si>
+    <t>0.2197,0.0033,0.8794,0.0011</t>
+  </si>
+  <si>
+    <t>0.0046,0.1805,0.9843,0.0006</t>
+  </si>
+  <si>
+    <t>0.9827,0.0154,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.9758,0.0034,0.0114,0.0028</t>
+  </si>
+  <si>
+    <t>0.9934,0.0018,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.0055,0.2342,0.9853,0.0105</t>
+  </si>
+  <si>
+    <t>0.9951,0.0010,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0013,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.0139,0.4125,0.9357,0.0042</t>
+  </si>
+  <si>
+    <t>0.0026,0.0681,0.9878,0.0033</t>
+  </si>
+  <si>
+    <t>0.0018,0.0051,0.9965,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.8330,0.9882,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0012,0.9980,0.0019</t>
+  </si>
+  <si>
+    <t>0.0110,0.9897,0.0088,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9961,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1135,0.0014,0.9416,0.0019</t>
+  </si>
+  <si>
+    <t>0.4420,0.0401,0.6022,0.0039</t>
+  </si>
+  <si>
+    <t>0.0095,0.0274,0.9829,0.0214</t>
+  </si>
+  <si>
+    <t>0.0029,0.7833,0.8899,0.0011</t>
+  </si>
+  <si>
+    <t>0.0023,0.5667,0.9681,0.0009</t>
+  </si>
+  <si>
+    <t>0.0022,0.9833,0.1365,0.0040</t>
+  </si>
+  <si>
+    <t>0.0011,0.9812,0.7705,0.0008</t>
+  </si>
+  <si>
+    <t>0.0126,0.0012,0.0024,0.9930</t>
+  </si>
+  <si>
+    <t>0.0014,0.0007,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.0167,0.0003,0.0001,0.9964</t>
+  </si>
+  <si>
+    <t>0.0046,0.0010,0.0007,0.9973</t>
+  </si>
+  <si>
+    <t>0.0067,0.0006,0.0001,0.9972</t>
+  </si>
+  <si>
+    <t>0.0033,0.0053,0.0010,0.9962</t>
+  </si>
+  <si>
+    <t>0.0012,0.9794,0.8957,0.0002</t>
+  </si>
+  <si>
+    <t>0.0109,0.6861,0.9526,0.0010</t>
+  </si>
+  <si>
+    <t>0.0169,0.8646,0.2286,0.0014</t>
+  </si>
+  <si>
+    <t>0.0018,0.9406,0.9247,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.8957,0.8734,0.0009</t>
+  </si>
+  <si>
+    <t>0.0043,0.8313,0.8916,0.0015</t>
+  </si>
+  <si>
+    <t>0.9930,0.0040,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9884,0.0117,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9921,0.0030,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9938,0.0027,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9977,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9932,0.0036,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9899,0.0079,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0018,0.0019,0.9964,0.0077</t>
+  </si>
+  <si>
+    <t>0.0017,0.0019,0.9964,0.0020</t>
+  </si>
+  <si>
+    <t>0.8614,0.0028,0.0127,0.0794</t>
+  </si>
+  <si>
+    <t>0.0009,0.0009,0.9983,0.0004</t>
+  </si>
+  <si>
+    <t>0.0212,0.9696,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.0022,0.9958,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0178,0.9791,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.1452,0.8928,0.0063,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.9875,0.0024,0.0005</t>
+  </si>
+  <si>
+    <t>0.0042,0.9918,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.3487,0.7748,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.8599,0.0711,0.0518,0.0074</t>
+  </si>
+  <si>
+    <t>0.5259,0.0072,0.3896,0.0352</t>
+  </si>
+  <si>
+    <t>0.6762,0.1735,0.1071,0.0328</t>
+  </si>
+  <si>
+    <t>0.4497,0.0154,0.6428,0.0046</t>
+  </si>
+  <si>
+    <t>0.0617,0.0269,0.1405,0.8859</t>
+  </si>
+  <si>
+    <t>0.0127,0.9755,0.0452,0.0013</t>
+  </si>
+  <si>
+    <t>0.0068,0.9792,0.0364,0.0104</t>
+  </si>
+  <si>
+    <t>0.0025,0.9931,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.0075,0.9702,0.2826,0.0053</t>
+  </si>
+  <si>
+    <t>0.0204,0.9732,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.2448,0.7111,0.1538,0.0052</t>
+  </si>
+  <si>
+    <t>0.8681,0.1604,0.0085,0.0017</t>
+  </si>
+  <si>
+    <t>0.9957,0.0006,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9956,0.0003,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.9936,0.0012,0.0005,0.0028</t>
+  </si>
+  <si>
+    <t>0.9943,0.0008,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9959,0.0015,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9938,0.0026,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.8878,0.9871,0.0002</t>
+  </si>
+  <si>
+    <t>0.0061,0.3213,0.9153,0.0015</t>
+  </si>
+  <si>
+    <t>0.0271,0.0294,0.9416,0.0030</t>
+  </si>
+  <si>
+    <t>0.0152,0.0054,0.9858,0.0003</t>
+  </si>
+  <si>
+    <t>0.9469,0.0169,0.0137,0.0059</t>
+  </si>
+  <si>
+    <t>0.9365,0.0013,0.0443,0.0030</t>
+  </si>
+  <si>
+    <t>0.3649,0.0007,0.8456,0.0006</t>
+  </si>
+  <si>
+    <t>0.6282,0.0414,0.3711,0.0269</t>
+  </si>
+  <si>
+    <t>0.0531,0.0002,0.0001,0.9904</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0035,0.0007,0.0004,0.9979</t>
+  </si>
+  <si>
+    <t>0.0072,0.0003,0.0014,0.9954</t>
+  </si>
+  <si>
+    <t>0.0049,0.7974,0.8972,0.0027</t>
+  </si>
+  <si>
+    <t>0.9947,0.0005,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.0360,0.9511,0.0036,0.0173</t>
+  </si>
+  <si>
+    <t>0.9927,0.0005,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.7274,0.3345,0.0170,0.0051</t>
+  </si>
+  <si>
+    <t>0.9894,0.0024,0.0015,0.0024</t>
+  </si>
+  <si>
+    <t>0.5690,0.0042,0.0008,0.6003</t>
+  </si>
+  <si>
+    <t>0.9951,0.0010,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.0026,0.1787,0.7050,0.1986</t>
+  </si>
+  <si>
+    <t>0.9733,0.0007,0.0012,0.0229</t>
+  </si>
+  <si>
+    <t>0.9891,0.0016,0.0030,0.0022</t>
+  </si>
+  <si>
+    <t>0.0888,0.9010,0.0260,0.0035</t>
+  </si>
+  <si>
+    <t>0.9370,0.0144,0.0303,0.0034</t>
+  </si>
+  <si>
+    <t>0.9705,0.0202,0.0046,0.0018</t>
+  </si>
+  <si>
+    <t>0.0290,0.5986,0.6350,0.0459</t>
+  </si>
+  <si>
+    <t>0.4598,0.1587,0.4442,0.0050</t>
+  </si>
+  <si>
+    <t>0.9576,0.0058,0.0327,0.0008</t>
+  </si>
+  <si>
+    <t>0.9882,0.0028,0.0005,0.0050</t>
+  </si>
+  <si>
+    <t>0.9943,0.0017,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9951,0.0015,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9969,0.0010,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9958,0.0008,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9903,0.0046,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9967,0.0005,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9947,0.0015,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9280,0.0992,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.6097,0.5296,0.0064,0.0009</t>
+  </si>
+  <si>
+    <t>0.8192,0.2652,0.0048,0.0008</t>
+  </si>
+  <si>
+    <t>0.0507,0.0443,0.9432,0.0213</t>
+  </si>
+  <si>
+    <t>0.9901,0.0053,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9922,0.0028,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9789,0.0130,0.0055,0.0021</t>
+  </si>
+  <si>
+    <t>0.9883,0.0047,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.0040,0.0666,0.9916,0.0031</t>
+  </si>
+  <si>
+    <t>0.9822,0.0246,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.0074,0.0024,0.9906,0.0011</t>
+  </si>
+  <si>
+    <t>0.0035,0.0566,0.9900,0.0038</t>
+  </si>
+  <si>
+    <t>0.0198,0.0014,0.9851,0.0015</t>
+  </si>
+  <si>
+    <t>0.0030,0.0382,0.9869,0.0072</t>
+  </si>
+  <si>
+    <t>0.0096,0.0084,0.9839,0.0024</t>
+  </si>
+  <si>
+    <t>0.0319,0.0007,0.9815,0.0013</t>
+  </si>
+  <si>
+    <t>0.0019,0.0033,0.9936,0.0038</t>
+  </si>
+  <si>
+    <t>0.0159,0.0171,0.9814,0.0071</t>
+  </si>
+  <si>
+    <t>0.2504,0.0029,0.8397,0.0026</t>
+  </si>
+  <si>
+    <t>0.1940,0.0590,0.7972,0.0203</t>
+  </si>
+  <si>
+    <t>0.1121,0.0795,0.7376,0.0032</t>
+  </si>
+  <si>
+    <t>0.0287,0.0223,0.9668,0.0008</t>
+  </si>
+  <si>
+    <t>0.6138,0.0017,0.5346,0.0004</t>
+  </si>
+  <si>
+    <t>0.2725,0.0367,0.7521,0.0043</t>
+  </si>
+  <si>
+    <t>0.2890,0.0191,0.8115,0.0031</t>
+  </si>
+  <si>
+    <t>0.0914,0.9358,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0498,0.9587,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9258,0.1283,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.7384,0.3962,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.3379,0.7875,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.8850,0.1235,0.0054,0.0013</t>
+  </si>
+  <si>
+    <t>0.9724,0.0005,0.0213,0.0006</t>
+  </si>
+  <si>
+    <t>0.9495,0.0129,0.0122,0.0060</t>
+  </si>
+  <si>
+    <t>0.7685,0.0149,0.2810,0.0053</t>
+  </si>
+  <si>
+    <t>0.8011,0.0040,0.1666,0.0153</t>
+  </si>
+  <si>
+    <t>0.0116,0.0097,0.9719,0.0140</t>
+  </si>
+  <si>
+    <t>0.1290,0.1707,0.6905,0.0724</t>
+  </si>
+  <si>
+    <t>0.0334,0.0217,0.9513,0.0078</t>
+  </si>
+  <si>
+    <t>0.6775,0.0061,0.3922,0.0031</t>
+  </si>
+  <si>
+    <t>0.0086,0.0305,0.9476,0.0147</t>
+  </si>
+  <si>
+    <t>0.9962,0.0010,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9959,0.0019,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9948,0.0023,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9918,0.0046,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0004,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9966,0.0004,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.0036,0.0169,0.9904,0.0062</t>
+  </si>
+  <si>
+    <t>0.2198,0.1520,0.7423,0.0208</t>
+  </si>
+  <si>
+    <t>0.8998,0.0125,0.0409,0.0196</t>
+  </si>
+  <si>
+    <t>0.0204,0.0042,0.9849,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.0021,0.9928,0.0058</t>
+  </si>
+  <si>
+    <t>0.0192,0.1522,0.9193,0.0030</t>
+  </si>
+  <si>
+    <t>0.0031,0.0119,0.9961,0.0015</t>
+  </si>
+  <si>
+    <t>0.0180,0.0053,0.9746,0.0062</t>
+  </si>
+  <si>
+    <t>0.0015,0.0033,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.0115,0.0101,0.9825,0.0004</t>
+  </si>
+  <si>
+    <t>0.1801,0.0252,0.8326,0.0128</t>
+  </si>
+  <si>
+    <t>0.8418,0.0014,0.2365,0.0013</t>
+  </si>
+  <si>
+    <t>0.7662,0.0029,0.2540,0.0095</t>
+  </si>
+  <si>
+    <t>0.9654,0.0019,0.0079,0.0069</t>
+  </si>
+  <si>
+    <t>0.9962,0.0018,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9916,0.0055,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9943,0.0011,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9887,0.0072,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9908,0.0015,0.0003,0.0055</t>
+  </si>
+  <si>
+    <t>0.9961,0.0013,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9967,0.0023,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9900,0.0025,0.0005,0.0039</t>
+  </si>
+  <si>
+    <t>0.0545,0.1171,0.7538,0.0052</t>
+  </si>
+  <si>
+    <t>0.0053,0.0154,0.9862,0.0064</t>
+  </si>
+  <si>
+    <t>0.0363,0.0193,0.9451,0.0064</t>
+  </si>
+  <si>
+    <t>0.0364,0.0046,0.9703,0.0015</t>
+  </si>
+  <si>
+    <t>0.0012,0.0005,0.9973,0.0009</t>
+  </si>
+  <si>
+    <t>0.1033,0.0344,0.7699,0.1692</t>
+  </si>
+  <si>
+    <t>0.0309,0.0175,0.9444,0.0231</t>
+  </si>
+  <si>
+    <t>0.2192,0.1072,0.3160,0.1605</t>
+  </si>
+  <si>
+    <t>0.9680,0.0009,0.0029,0.0207</t>
+  </si>
+  <si>
+    <t>0.0185,0.0152,0.0042,0.9856</t>
+  </si>
+  <si>
+    <t>0.0104,0.0013,0.0003,0.9957</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.8942,0.0062,0.0097,0.1037</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2287,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2816,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>327</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3908,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,10 +4118,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4401,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,10 +4748,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,10 +4888,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,10 +5420,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5434,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
